--- a/Ammoniak/Ammoniak_Brownfield_H2_Leuna/Datenbank.xlsx
+++ b/Ammoniak/Ammoniak_Brownfield_H2_Leuna/Datenbank.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_Höchst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Ammoniak\Ammoniak_Brownfield_H2_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2705806A-820F-4FE4-8CCD-A611B41F9BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871C98CE-3B07-45CD-AB04-DD65888CC7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-53868" yWindow="3444" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="300">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1001,12 +1001,6 @@
   </si>
   <si>
     <t>calc_cost_nh3</t>
-  </si>
-  <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
   </si>
   <si>
     <t>Verkaufspreiseanalyse</t>
@@ -1204,7 +1198,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1262,7 +1256,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1319,16 +1312,16 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1339,29 +1332,29 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1703,10 +1696,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="70" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1723,8 +1716,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="61"/>
-      <c r="B3" s="72"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="71"/>
       <c r="C3" t="s">
         <v>102</v>
       </c>
@@ -1739,8 +1732,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="61"/>
-      <c r="B4" s="72"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="71"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
@@ -1748,15 +1741,15 @@
         <v>28</v>
       </c>
       <c r="E4" s="20">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="61"/>
-      <c r="B5" s="72"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="71"/>
       <c r="C5" t="s">
         <v>13</v>
       </c>
@@ -1771,8 +1764,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="61"/>
-      <c r="B6" s="72"/>
+      <c r="A6" s="60"/>
+      <c r="B6" s="71"/>
       <c r="C6" t="s">
         <v>15</v>
       </c>
@@ -1787,8 +1780,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="61"/>
-      <c r="B7" s="72"/>
+      <c r="A7" s="60"/>
+      <c r="B7" s="71"/>
       <c r="C7" t="s">
         <v>17</v>
       </c>
@@ -1803,8 +1796,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="61"/>
-      <c r="B8" s="73" t="s">
+      <c r="A8" s="60"/>
+      <c r="B8" s="72" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1821,8 +1814,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="61"/>
-      <c r="B9" s="72"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="71"/>
       <c r="C9" t="s">
         <v>105</v>
       </c>
@@ -1837,8 +1830,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="61"/>
-      <c r="B10" s="72"/>
+      <c r="A10" s="60"/>
+      <c r="B10" s="71"/>
       <c r="C10" t="s">
         <v>12</v>
       </c>
@@ -1853,8 +1846,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="61"/>
-      <c r="B11" s="72"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="71"/>
       <c r="C11" t="s">
         <v>13</v>
       </c>
@@ -1869,8 +1862,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="61"/>
-      <c r="B12" s="72"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="71"/>
       <c r="C12" t="s">
         <v>110</v>
       </c>
@@ -1885,8 +1878,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="61"/>
-      <c r="B13" s="72"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="71"/>
       <c r="C13" t="s">
         <v>109</v>
       </c>
@@ -1901,8 +1894,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="61"/>
-      <c r="B14" s="72"/>
+      <c r="A14" s="60"/>
+      <c r="B14" s="71"/>
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -1917,8 +1910,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="61"/>
-      <c r="B15" s="74"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="73"/>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
@@ -1933,8 +1926,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="61"/>
-      <c r="B16" s="65" t="s">
+      <c r="A16" s="60"/>
+      <c r="B16" s="64" t="s">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -1952,8 +1945,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="61"/>
-      <c r="B17" s="65"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="64"/>
       <c r="C17" t="s">
         <v>12</v>
       </c>
@@ -1968,8 +1961,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="61"/>
-      <c r="B18" s="65"/>
+      <c r="A18" s="60"/>
+      <c r="B18" s="64"/>
       <c r="C18" t="s">
         <v>13</v>
       </c>
@@ -1984,8 +1977,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="61"/>
-      <c r="B19" s="65"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="64"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -2000,8 +1993,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="61"/>
-      <c r="B20" s="65"/>
+      <c r="A20" s="60"/>
+      <c r="B20" s="64"/>
       <c r="C20" t="s">
         <v>17</v>
       </c>
@@ -2016,10 +2009,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="60" t="s">
+      <c r="A21" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="64" t="s">
+      <c r="B21" s="63" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2036,8 +2029,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="61"/>
-      <c r="B22" s="65"/>
+      <c r="A22" s="60"/>
+      <c r="B22" s="64"/>
       <c r="C22" t="s">
         <v>13</v>
       </c>
@@ -2052,8 +2045,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="61"/>
-      <c r="B23" s="65"/>
+      <c r="A23" s="60"/>
+      <c r="B23" s="64"/>
       <c r="C23" t="s">
         <v>15</v>
       </c>
@@ -2068,8 +2061,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="61"/>
-      <c r="B24" s="65"/>
+      <c r="A24" s="60"/>
+      <c r="B24" s="64"/>
       <c r="C24" t="s">
         <v>22</v>
       </c>
@@ -2084,8 +2077,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="61"/>
-      <c r="B25" s="65"/>
+      <c r="A25" s="60"/>
+      <c r="B25" s="64"/>
       <c r="C25" t="s">
         <v>47</v>
       </c>
@@ -2100,8 +2093,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="61"/>
-      <c r="B26" s="65"/>
+      <c r="A26" s="60"/>
+      <c r="B26" s="64"/>
       <c r="C26" t="s">
         <v>48</v>
       </c>
@@ -2116,8 +2109,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="61"/>
-      <c r="B27" s="65"/>
+      <c r="A27" s="60"/>
+      <c r="B27" s="64"/>
       <c r="C27" t="s">
         <v>17</v>
       </c>
@@ -2132,8 +2125,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="61"/>
-      <c r="B28" s="65"/>
+      <c r="A28" s="60"/>
+      <c r="B28" s="64"/>
       <c r="C28" t="s">
         <v>114</v>
       </c>
@@ -2148,8 +2141,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="61"/>
-      <c r="B29" s="66" t="s">
+      <c r="A29" s="60"/>
+      <c r="B29" s="65" t="s">
         <v>256</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -2166,8 +2159,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="61"/>
-      <c r="B30" s="69"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="68"/>
       <c r="C30" s="48" t="s">
         <v>23</v>
       </c>
@@ -2183,8 +2176,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="61"/>
-      <c r="B31" s="69"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="68"/>
       <c r="C31" s="48" t="s">
         <v>18</v>
       </c>
@@ -2199,8 +2192,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="61"/>
-      <c r="B32" s="69"/>
+      <c r="A32" s="60"/>
+      <c r="B32" s="68"/>
       <c r="C32" s="48" t="s">
         <v>19</v>
       </c>
@@ -2215,8 +2208,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
-      <c r="B33" s="69"/>
+      <c r="A33" s="60"/>
+      <c r="B33" s="68"/>
       <c r="C33" s="48" t="s">
         <v>47</v>
       </c>
@@ -2231,8 +2224,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="61"/>
-      <c r="B34" s="69"/>
+      <c r="A34" s="60"/>
+      <c r="B34" s="68"/>
       <c r="C34" s="48" t="s">
         <v>48</v>
       </c>
@@ -2247,8 +2240,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
-      <c r="B35" s="69"/>
+      <c r="A35" s="60"/>
+      <c r="B35" s="68"/>
       <c r="C35" s="48" t="s">
         <v>115</v>
       </c>
@@ -2263,8 +2256,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="61"/>
-      <c r="B36" s="69"/>
+      <c r="A36" s="60"/>
+      <c r="B36" s="68"/>
       <c r="C36" s="48" t="s">
         <v>114</v>
       </c>
@@ -2279,8 +2272,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="61"/>
-      <c r="B37" s="69"/>
+      <c r="A37" s="60"/>
+      <c r="B37" s="68"/>
       <c r="C37" s="48" t="s">
         <v>15</v>
       </c>
@@ -2295,8 +2288,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="62"/>
-      <c r="B38" s="70"/>
+      <c r="A38" s="61"/>
+      <c r="B38" s="69"/>
       <c r="C38" s="14" t="s">
         <v>17</v>
       </c>
@@ -2311,46 +2304,46 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="60" t="s">
+      <c r="A39" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="55" t="s">
+      <c r="C39" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="55" t="s">
+      <c r="D39" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="56">
+      <c r="E39" s="55">
         <v>0.1699</v>
       </c>
-      <c r="F39" s="55" t="s">
+      <c r="F39" s="54" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="63"/>
-      <c r="B40" s="57" t="s">
+      <c r="A40" s="62"/>
+      <c r="B40" s="56" t="s">
+        <v>295</v>
+      </c>
+      <c r="C40" s="57" t="s">
+        <v>296</v>
+      </c>
+      <c r="D40" s="57" t="s">
         <v>297</v>
       </c>
-      <c r="C40" s="58" t="s">
-        <v>298</v>
-      </c>
-      <c r="D40" s="58" t="s">
-        <v>299</v>
-      </c>
-      <c r="E40" s="59">
+      <c r="E40" s="58">
         <v>5</v>
       </c>
-      <c r="F40" s="58" t="s">
+      <c r="F40" s="57" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="61"/>
-      <c r="B41" s="66" t="s">
+      <c r="A41" s="60"/>
+      <c r="B41" s="65" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="4" t="s">
@@ -2367,8 +2360,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="61"/>
-      <c r="B42" s="65"/>
+      <c r="A42" s="60"/>
+      <c r="B42" s="64"/>
       <c r="C42" t="s">
         <v>12</v>
       </c>
@@ -2383,8 +2376,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="61"/>
-      <c r="B43" s="65"/>
+      <c r="A43" s="60"/>
+      <c r="B43" s="64"/>
       <c r="C43" t="s">
         <v>19</v>
       </c>
@@ -2399,8 +2392,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="61"/>
-      <c r="B44" s="65"/>
+      <c r="A44" s="60"/>
+      <c r="B44" s="64"/>
       <c r="C44" t="s">
         <v>20</v>
       </c>
@@ -2415,8 +2408,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="61"/>
-      <c r="B45" s="65"/>
+      <c r="A45" s="60"/>
+      <c r="B45" s="64"/>
       <c r="C45" t="s">
         <v>15</v>
       </c>
@@ -2431,8 +2424,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="61"/>
-      <c r="B46" s="65"/>
+      <c r="A46" s="60"/>
+      <c r="B46" s="64"/>
       <c r="C46" t="s">
         <v>82</v>
       </c>
@@ -2447,8 +2440,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="61"/>
-      <c r="B47" s="67"/>
+      <c r="A47" s="60"/>
+      <c r="B47" s="66"/>
       <c r="C47" s="5" t="s">
         <v>17</v>
       </c>
@@ -2463,8 +2456,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="61"/>
-      <c r="B48" s="66" t="s">
+      <c r="A48" s="60"/>
+      <c r="B48" s="65" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -2481,8 +2474,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="61"/>
-      <c r="B49" s="65"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="64"/>
       <c r="C49" t="s">
         <v>12</v>
       </c>
@@ -2497,8 +2490,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="61"/>
-      <c r="B50" s="65"/>
+      <c r="A50" s="60"/>
+      <c r="B50" s="64"/>
       <c r="C50" t="s">
         <v>19</v>
       </c>
@@ -2513,8 +2506,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="61"/>
-      <c r="B51" s="65"/>
+      <c r="A51" s="60"/>
+      <c r="B51" s="64"/>
       <c r="C51" t="s">
         <v>20</v>
       </c>
@@ -2529,8 +2522,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="61"/>
-      <c r="B52" s="65"/>
+      <c r="A52" s="60"/>
+      <c r="B52" s="64"/>
       <c r="C52" t="s">
         <v>15</v>
       </c>
@@ -2545,8 +2538,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="61"/>
-      <c r="B53" s="65"/>
+      <c r="A53" s="60"/>
+      <c r="B53" s="64"/>
       <c r="C53" t="s">
         <v>82</v>
       </c>
@@ -2561,8 +2554,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="62"/>
-      <c r="B54" s="68"/>
+      <c r="A54" s="61"/>
+      <c r="B54" s="67"/>
       <c r="C54" s="14" t="s">
         <v>17</v>
       </c>
@@ -2577,7 +2570,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="60" t="s">
+      <c r="A55" s="59" t="s">
         <v>90</v>
       </c>
       <c r="B55" s="16" t="s">
@@ -2590,14 +2583,14 @@
         <v>92</v>
       </c>
       <c r="E55" s="3">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
+      <c r="A56" s="60"/>
       <c r="B56" s="17" t="s">
         <v>93</v>
       </c>
@@ -2615,7 +2608,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="62"/>
+      <c r="A57" s="61"/>
       <c r="B57" s="1" t="s">
         <v>94</v>
       </c>
@@ -2654,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="12" customWidth="1"/>
@@ -2687,7 +2680,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="78" t="s">
         <v>84</v>
       </c>
       <c r="B2" s="82" t="s">
@@ -2705,8 +2698,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="81"/>
-      <c r="B3" s="76"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="12" t="s">
         <v>135</v>
       </c>
@@ -2719,8 +2712,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="81"/>
-      <c r="B4" s="76"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="12" t="s">
         <v>102</v>
       </c>
@@ -2733,8 +2726,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="81"/>
-      <c r="B5" s="76"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="84"/>
       <c r="C5" s="12" t="s">
         <v>171</v>
       </c>
@@ -2747,8 +2740,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="81"/>
-      <c r="B6" s="76"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="84"/>
       <c r="C6" s="12" t="s">
         <v>183</v>
       </c>
@@ -2761,8 +2754,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="81"/>
-      <c r="B7" s="76"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="12" t="s">
         <v>201</v>
       </c>
@@ -2775,8 +2768,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="81"/>
-      <c r="B8" s="76"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="84"/>
       <c r="C8" s="12" t="s">
         <v>249</v>
       </c>
@@ -2789,8 +2782,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="81"/>
-      <c r="B9" s="76"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="12" t="s">
         <v>215</v>
       </c>
@@ -2803,8 +2796,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="81"/>
-      <c r="B10" s="76"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="84"/>
       <c r="C10" s="12" t="s">
         <v>239</v>
       </c>
@@ -2817,13 +2810,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="81"/>
-      <c r="B11" s="76"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="84"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="81"/>
-      <c r="B12" s="75" t="s">
+      <c r="A12" s="80"/>
+      <c r="B12" s="86" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="36" t="s">
@@ -2838,8 +2831,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="81"/>
-      <c r="B13" s="76"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="12" t="s">
         <v>176</v>
       </c>
@@ -2852,8 +2845,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="81"/>
-      <c r="B14" s="76"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="12" t="s">
         <v>179</v>
       </c>
@@ -2866,8 +2859,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="81"/>
-      <c r="B15" s="76"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="12" t="s">
         <v>180</v>
       </c>
@@ -2880,8 +2873,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="81"/>
-      <c r="B16" s="76"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="12" t="s">
         <v>102</v>
       </c>
@@ -2894,8 +2887,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="81"/>
-      <c r="B17" s="76"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="12" t="s">
         <v>183</v>
       </c>
@@ -2908,8 +2901,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="81"/>
-      <c r="B18" s="76"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="12" t="s">
         <v>201</v>
       </c>
@@ -2922,8 +2915,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="81"/>
-      <c r="B19" s="76"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="12" t="s">
         <v>249</v>
       </c>
@@ -2936,8 +2929,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="81"/>
-      <c r="B20" s="76"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="84"/>
       <c r="C20" s="12" t="s">
         <v>215</v>
       </c>
@@ -2950,8 +2943,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="81"/>
-      <c r="B21" s="76"/>
+      <c r="A21" s="80"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="12" t="s">
         <v>239</v>
       </c>
@@ -2964,16 +2957,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="81"/>
-      <c r="B22" s="78"/>
+      <c r="A22" s="80"/>
+      <c r="B22" s="85"/>
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
       <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="81"/>
-      <c r="B23" s="83" t="s">
+      <c r="A23" s="80"/>
+      <c r="B23" s="75" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -2988,8 +2981,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="81"/>
-      <c r="B24" s="83"/>
+      <c r="A24" s="80"/>
+      <c r="B24" s="75"/>
       <c r="C24" s="12" t="s">
         <v>135</v>
       </c>
@@ -3002,8 +2995,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="81"/>
-      <c r="B25" s="83"/>
+      <c r="A25" s="80"/>
+      <c r="B25" s="75"/>
       <c r="C25" s="12" t="s">
         <v>102</v>
       </c>
@@ -3016,8 +3009,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="81"/>
-      <c r="B26" s="83"/>
+      <c r="A26" s="80"/>
+      <c r="B26" s="75"/>
       <c r="C26" s="12" t="s">
         <v>173</v>
       </c>
@@ -3030,8 +3023,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="81"/>
-      <c r="B27" s="83"/>
+      <c r="A27" s="80"/>
+      <c r="B27" s="75"/>
       <c r="C27" s="12" t="s">
         <v>183</v>
       </c>
@@ -3044,8 +3037,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="81"/>
-      <c r="B28" s="83"/>
+      <c r="A28" s="80"/>
+      <c r="B28" s="75"/>
       <c r="C28" s="12" t="s">
         <v>201</v>
       </c>
@@ -3058,8 +3051,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="81"/>
-      <c r="B29" s="83"/>
+      <c r="A29" s="80"/>
+      <c r="B29" s="75"/>
       <c r="C29" s="12" t="s">
         <v>249</v>
       </c>
@@ -3072,8 +3065,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="81"/>
-      <c r="B30" s="83"/>
+      <c r="A30" s="80"/>
+      <c r="B30" s="75"/>
       <c r="C30" s="12" t="s">
         <v>215</v>
       </c>
@@ -3086,8 +3079,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="81"/>
-      <c r="B31" s="83"/>
+      <c r="A31" s="80"/>
+      <c r="B31" s="75"/>
       <c r="C31" s="12" t="s">
         <v>239</v>
       </c>
@@ -3100,15 +3093,15 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="81"/>
-      <c r="B32" s="83"/>
+      <c r="A32" s="80"/>
+      <c r="B32" s="75"/>
       <c r="E32" s="34"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="79" t="s">
+      <c r="A33" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="85" t="s">
+      <c r="B33" s="87" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="27" t="s">
@@ -3119,12 +3112,12 @@
       </c>
       <c r="E33" s="40"/>
       <c r="F33" s="27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="81"/>
-      <c r="B34" s="83"/>
+      <c r="A34" s="80"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="12" t="s">
         <v>139</v>
       </c>
@@ -3133,12 +3126,12 @@
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="81"/>
-      <c r="B35" s="83"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="75"/>
       <c r="C35" s="12" t="s">
         <v>168</v>
       </c>
@@ -3151,8 +3144,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="81"/>
-      <c r="B36" s="83"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="75"/>
       <c r="C36" s="12" t="s">
         <v>169</v>
       </c>
@@ -3165,8 +3158,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="81"/>
-      <c r="B37" s="83"/>
+      <c r="A37" s="80"/>
+      <c r="B37" s="75"/>
       <c r="C37" s="12" t="s">
         <v>183</v>
       </c>
@@ -3179,8 +3172,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="81"/>
-      <c r="B38" s="83"/>
+      <c r="A38" s="80"/>
+      <c r="B38" s="75"/>
       <c r="C38" s="12" t="s">
         <v>201</v>
       </c>
@@ -3193,8 +3186,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="81"/>
-      <c r="B39" s="83"/>
+      <c r="A39" s="80"/>
+      <c r="B39" s="75"/>
       <c r="C39" s="12" t="s">
         <v>249</v>
       </c>
@@ -3207,8 +3200,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="81"/>
-      <c r="B40" s="83"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="75"/>
       <c r="C40" s="12" t="s">
         <v>215</v>
       </c>
@@ -3221,8 +3214,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="81"/>
-      <c r="B41" s="83"/>
+      <c r="A41" s="80"/>
+      <c r="B41" s="75"/>
       <c r="C41" s="12" t="s">
         <v>239</v>
       </c>
@@ -3235,13 +3228,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="81"/>
-      <c r="B42" s="83"/>
+      <c r="A42" s="80"/>
+      <c r="B42" s="75"/>
       <c r="E42" s="34"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="81"/>
-      <c r="B43" s="86" t="s">
+      <c r="A43" s="80"/>
+      <c r="B43" s="74" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="36" t="s">
@@ -3256,8 +3249,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="81"/>
-      <c r="B44" s="83"/>
+      <c r="A44" s="80"/>
+      <c r="B44" s="75"/>
       <c r="C44" s="12" t="s">
         <v>141</v>
       </c>
@@ -3270,8 +3263,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="81"/>
-      <c r="B45" s="76"/>
+      <c r="A45" s="80"/>
+      <c r="B45" s="84"/>
       <c r="C45" s="12" t="s">
         <v>139</v>
       </c>
@@ -3284,8 +3277,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="81"/>
-      <c r="B46" s="76"/>
+      <c r="A46" s="80"/>
+      <c r="B46" s="84"/>
       <c r="C46" s="12" t="s">
         <v>135</v>
       </c>
@@ -3298,8 +3291,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="81"/>
-      <c r="B47" s="76"/>
+      <c r="A47" s="80"/>
+      <c r="B47" s="84"/>
       <c r="C47" s="12" t="s">
         <v>156</v>
       </c>
@@ -3312,8 +3305,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="81"/>
-      <c r="B48" s="76"/>
+      <c r="A48" s="80"/>
+      <c r="B48" s="84"/>
       <c r="C48" s="12" t="s">
         <v>157</v>
       </c>
@@ -3326,8 +3319,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="81"/>
-      <c r="B49" s="76"/>
+      <c r="A49" s="80"/>
+      <c r="B49" s="84"/>
       <c r="C49" s="12" t="s">
         <v>183</v>
       </c>
@@ -3340,8 +3333,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="81"/>
-      <c r="B50" s="76"/>
+      <c r="A50" s="80"/>
+      <c r="B50" s="84"/>
       <c r="C50" s="12" t="s">
         <v>201</v>
       </c>
@@ -3354,8 +3347,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="81"/>
-      <c r="B51" s="76"/>
+      <c r="A51" s="80"/>
+      <c r="B51" s="84"/>
       <c r="C51" s="12" t="s">
         <v>249</v>
       </c>
@@ -3368,8 +3361,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="81"/>
-      <c r="B52" s="76"/>
+      <c r="A52" s="80"/>
+      <c r="B52" s="84"/>
       <c r="C52" s="12" t="s">
         <v>215</v>
       </c>
@@ -3382,8 +3375,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="81"/>
-      <c r="B53" s="76"/>
+      <c r="A53" s="80"/>
+      <c r="B53" s="84"/>
       <c r="C53" s="12" t="s">
         <v>239</v>
       </c>
@@ -3396,15 +3389,15 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="84"/>
-      <c r="B54" s="87"/>
+      <c r="A54" s="81"/>
+      <c r="B54" s="88"/>
       <c r="C54" s="42"/>
       <c r="D54" s="42"/>
       <c r="E54" s="43"/>
       <c r="F54" s="42"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="79" t="s">
+      <c r="A55" s="78" t="s">
         <v>86</v>
       </c>
       <c r="B55" s="82" t="s">
@@ -3422,8 +3415,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="81"/>
-      <c r="B56" s="76"/>
+      <c r="A56" s="80"/>
+      <c r="B56" s="84"/>
       <c r="C56" s="12" t="s">
         <v>199</v>
       </c>
@@ -3436,13 +3429,13 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="81"/>
-      <c r="B57" s="78"/>
+      <c r="A57" s="80"/>
+      <c r="B57" s="85"/>
       <c r="E57" s="32"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="81"/>
-      <c r="B58" s="86" t="s">
+      <c r="A58" s="80"/>
+      <c r="B58" s="74" t="s">
         <v>6</v>
       </c>
       <c r="C58" s="36" t="s">
@@ -3457,8 +3450,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="81"/>
-      <c r="B59" s="83"/>
+      <c r="A59" s="80"/>
+      <c r="B59" s="75"/>
       <c r="C59" s="12" t="s">
         <v>135</v>
       </c>
@@ -3471,8 +3464,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="81"/>
-      <c r="B60" s="83"/>
+      <c r="A60" s="80"/>
+      <c r="B60" s="75"/>
       <c r="C60" s="12" t="s">
         <v>151</v>
       </c>
@@ -3485,8 +3478,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="81"/>
-      <c r="B61" s="83"/>
+      <c r="A61" s="80"/>
+      <c r="B61" s="75"/>
       <c r="C61" s="12" t="s">
         <v>183</v>
       </c>
@@ -3499,8 +3492,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="81"/>
-      <c r="B62" s="83"/>
+      <c r="A62" s="80"/>
+      <c r="B62" s="75"/>
       <c r="C62" s="12" t="s">
         <v>201</v>
       </c>
@@ -3513,8 +3506,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="81"/>
-      <c r="B63" s="83"/>
+      <c r="A63" s="80"/>
+      <c r="B63" s="75"/>
       <c r="C63" s="12" t="s">
         <v>209</v>
       </c>
@@ -3527,8 +3520,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="81"/>
-      <c r="B64" s="83"/>
+      <c r="A64" s="80"/>
+      <c r="B64" s="75"/>
       <c r="C64" s="12" t="s">
         <v>249</v>
       </c>
@@ -3541,8 +3534,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="81"/>
-      <c r="B65" s="83"/>
+      <c r="A65" s="80"/>
+      <c r="B65" s="75"/>
       <c r="C65" s="12" t="s">
         <v>215</v>
       </c>
@@ -3555,8 +3548,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="81"/>
-      <c r="B66" s="83"/>
+      <c r="A66" s="80"/>
+      <c r="B66" s="75"/>
       <c r="C66" s="12" t="s">
         <v>239</v>
       </c>
@@ -3569,12 +3562,12 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="81"/>
-      <c r="B67" s="88"/>
+      <c r="A67" s="80"/>
+      <c r="B67" s="76"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="81"/>
-      <c r="B68" s="86" t="s">
+      <c r="A68" s="80"/>
+      <c r="B68" s="74" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="36" t="s">
@@ -3589,8 +3582,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="81"/>
-      <c r="B69" s="83"/>
+      <c r="A69" s="80"/>
+      <c r="B69" s="75"/>
       <c r="C69" s="12" t="s">
         <v>136</v>
       </c>
@@ -3603,8 +3596,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="81"/>
-      <c r="B70" s="83"/>
+      <c r="A70" s="80"/>
+      <c r="B70" s="75"/>
       <c r="C70" s="12" t="s">
         <v>149</v>
       </c>
@@ -3617,8 +3610,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="81"/>
-      <c r="B71" s="83"/>
+      <c r="A71" s="80"/>
+      <c r="B71" s="75"/>
       <c r="C71" s="12" t="s">
         <v>183</v>
       </c>
@@ -3631,8 +3624,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="81"/>
-      <c r="B72" s="83"/>
+      <c r="A72" s="80"/>
+      <c r="B72" s="75"/>
       <c r="C72" s="12" t="s">
         <v>201</v>
       </c>
@@ -3645,8 +3638,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="81"/>
-      <c r="B73" s="83"/>
+      <c r="A73" s="80"/>
+      <c r="B73" s="75"/>
       <c r="C73" s="12" t="s">
         <v>209</v>
       </c>
@@ -3659,8 +3652,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="81"/>
-      <c r="B74" s="83"/>
+      <c r="A74" s="80"/>
+      <c r="B74" s="75"/>
       <c r="C74" s="12" t="s">
         <v>249</v>
       </c>
@@ -3673,8 +3666,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="81"/>
-      <c r="B75" s="83"/>
+      <c r="A75" s="80"/>
+      <c r="B75" s="75"/>
       <c r="C75" s="12" t="s">
         <v>215</v>
       </c>
@@ -3687,8 +3680,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="81"/>
-      <c r="B76" s="83"/>
+      <c r="A76" s="80"/>
+      <c r="B76" s="75"/>
       <c r="C76" s="12" t="s">
         <v>239</v>
       </c>
@@ -3701,11 +3694,11 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="84"/>
-      <c r="B77" s="89"/>
+      <c r="A77" s="81"/>
+      <c r="B77" s="77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="79" t="s">
+      <c r="A78" s="78" t="s">
         <v>90</v>
       </c>
       <c r="B78" s="82" t="s">
@@ -3724,312 +3717,312 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="80"/>
-      <c r="B79" s="77"/>
-      <c r="C79" s="52" t="s">
-        <v>291</v>
-      </c>
-      <c r="D79" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="E79" s="53"/>
-      <c r="F79" s="52" t="s">
+      <c r="B79" s="84"/>
+      <c r="C79" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="E79" s="34"/>
+      <c r="F79" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="81"/>
-      <c r="B80" s="76"/>
-      <c r="C80" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>191</v>
-      </c>
+      <c r="A80" s="80"/>
+      <c r="B80" s="85"/>
       <c r="E80" s="34"/>
-      <c r="F80" s="12" t="s">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="80"/>
+      <c r="B81" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="C81" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="E81" s="41"/>
+      <c r="F81" s="36" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="80"/>
+      <c r="B82" s="84"/>
+      <c r="C82" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="E82" s="34"/>
+      <c r="F82" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="81"/>
-      <c r="B81" s="78"/>
-      <c r="E81" s="34"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="81"/>
-      <c r="B82" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="D82" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E82" s="41"/>
-      <c r="F82" s="36" t="s">
-        <v>163</v>
-      </c>
-    </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="81"/>
-      <c r="B83" s="76"/>
-      <c r="C83" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E83" s="34"/>
-      <c r="F83" s="12" t="s">
-        <v>194</v>
-      </c>
+      <c r="A83" s="80"/>
+      <c r="B83" s="85"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="39"/>
+      <c r="F83" s="38"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="81"/>
-      <c r="B84" s="78"/>
-      <c r="C84" s="38"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="39"/>
-      <c r="F84" s="38"/>
+      <c r="A84" s="80"/>
+      <c r="B84" s="86" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E84" s="34"/>
+      <c r="F84" s="12" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="81"/>
-      <c r="B85" s="75" t="s">
-        <v>94</v>
-      </c>
+      <c r="A85" s="80"/>
+      <c r="B85" s="84"/>
       <c r="C85" s="12" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E85" s="34"/>
       <c r="F85" s="12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="81"/>
-      <c r="B86" s="76"/>
-      <c r="C86" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D86" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="E86" s="34"/>
-      <c r="F86" s="12" t="s">
+      <c r="B86" s="88"/>
+      <c r="C86" s="42"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="43"/>
+      <c r="F86" s="42"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="78" t="s">
+        <v>211</v>
+      </c>
+      <c r="B87" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="79"/>
+      <c r="B88" s="84"/>
+      <c r="C88" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="F88" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="79"/>
+      <c r="B89" s="85"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="79"/>
+      <c r="B90" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F90" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="84"/>
-      <c r="B87" s="87"/>
-      <c r="C87" s="42"/>
-      <c r="D87" s="42"/>
-      <c r="E87" s="43"/>
-      <c r="F87" s="42"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="79" t="s">
-        <v>211</v>
-      </c>
-      <c r="B88" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="D88" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="80"/>
-      <c r="B89" s="76"/>
-      <c r="C89" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="80"/>
-      <c r="B90" s="78"/>
-      <c r="C90" s="38"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="38"/>
-    </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="80"/>
-      <c r="B91" s="75" t="s">
-        <v>234</v>
-      </c>
+      <c r="A91" s="79"/>
+      <c r="B91" s="84"/>
       <c r="C91" s="12" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F91" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="80"/>
-      <c r="B92" s="76"/>
+      <c r="A92" s="79"/>
+      <c r="B92" s="84"/>
       <c r="C92" s="12" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F92" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="80"/>
-      <c r="B93" s="76"/>
+      <c r="A93" s="79"/>
+      <c r="B93" s="84"/>
       <c r="C93" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F93" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="80"/>
-      <c r="B94" s="76"/>
+      <c r="A94" s="79"/>
+      <c r="B94" s="84"/>
       <c r="C94" s="12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F94" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="80"/>
-      <c r="B95" s="76"/>
+      <c r="A95" s="79"/>
+      <c r="B95" s="84"/>
       <c r="C95" s="12" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F95" s="12" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="80"/>
-      <c r="B96" s="76"/>
-      <c r="C96" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="F96" s="12" t="s">
-        <v>194</v>
+      <c r="A96" s="79"/>
+      <c r="B96" s="86" t="s">
+        <v>263</v>
+      </c>
+      <c r="C96" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="D96" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="E96" s="36"/>
+      <c r="F96" s="36" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="80"/>
-      <c r="B97" s="75" t="s">
-        <v>263</v>
-      </c>
-      <c r="C97" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="D97" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="E97" s="36"/>
-      <c r="F97" s="36" t="s">
+      <c r="A97" s="79"/>
+      <c r="B97" s="83"/>
+      <c r="C97" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="D97" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="E97" s="52"/>
+      <c r="F97" s="52" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="80"/>
-      <c r="B98" s="77"/>
+      <c r="A98" s="79"/>
+      <c r="B98" s="83"/>
       <c r="C98" s="52" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D98" s="52" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E98" s="52"/>
       <c r="F98" s="52" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="80"/>
-      <c r="B99" s="77"/>
+      <c r="A99" s="79"/>
+      <c r="B99" s="83"/>
       <c r="C99" s="52" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D99" s="52" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E99" s="52"/>
       <c r="F99" s="52" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="80"/>
-      <c r="B100" s="77"/>
+      <c r="A100" s="79"/>
+      <c r="B100" s="83"/>
       <c r="C100" s="52" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="D100" s="52" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="E100" s="52"/>
       <c r="F100" s="52" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="80"/>
-      <c r="B101" s="77"/>
+      <c r="A101" s="79"/>
+      <c r="B101" s="83"/>
       <c r="C101" s="52" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D101" s="52" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E101" s="52"/>
       <c r="F101" s="52" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="80"/>
-      <c r="B102" s="77"/>
+      <c r="A102" s="79"/>
+      <c r="B102" s="83"/>
       <c r="C102" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="D102" s="52" t="s">
-        <v>268</v>
+        <v>257</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>279</v>
       </c>
       <c r="E102" s="52"/>
       <c r="F102" s="52" t="s">
@@ -4037,71 +4030,71 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="80"/>
-      <c r="B103" s="77"/>
+      <c r="A103" s="79"/>
+      <c r="B103" s="83"/>
       <c r="C103" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>279</v>
+        <v>261</v>
+      </c>
+      <c r="D103" s="52" t="s">
+        <v>270</v>
       </c>
       <c r="E103" s="52"/>
-      <c r="F103" s="52" t="s">
+      <c r="F103" s="12" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="80"/>
-      <c r="B104" s="77"/>
+      <c r="A104" s="79"/>
+      <c r="B104" s="83"/>
       <c r="C104" s="52" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D104" s="52" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E104" s="52"/>
-      <c r="F104" s="12" t="s">
+      <c r="F104" s="52" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="79"/>
+      <c r="B105" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="C105" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="D105" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E105" s="36"/>
+      <c r="F105" s="36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="79"/>
+      <c r="B106" s="83"/>
+      <c r="C106" s="52" t="s">
+        <v>284</v>
+      </c>
+      <c r="D106" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="80"/>
-      <c r="B105" s="77"/>
-      <c r="C105" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="D105" s="52" t="s">
-        <v>271</v>
-      </c>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="80"/>
-      <c r="B106" s="75" t="s">
-        <v>281</v>
-      </c>
-      <c r="C106" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="D106" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36" t="s">
-        <v>265</v>
-      </c>
-    </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="80"/>
-      <c r="B107" s="77"/>
+      <c r="A107" s="79"/>
+      <c r="B107" s="83"/>
       <c r="C107" s="52" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D107" s="52" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E107" s="52"/>
       <c r="F107" s="52" t="s">
@@ -4109,78 +4102,59 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="80"/>
-      <c r="B108" s="77"/>
-      <c r="C108" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="D108" s="52" t="s">
-        <v>288</v>
-      </c>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52" t="s">
-        <v>269</v>
+      <c r="A108" s="79"/>
+      <c r="B108" s="83"/>
+      <c r="C108" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="80"/>
-      <c r="B109" s="77"/>
-      <c r="C109" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="F109" s="12" t="s">
-        <v>272</v>
-      </c>
+      <c r="A109" s="79"/>
+      <c r="B109" s="85"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="80"/>
-      <c r="B110" s="78"/>
+      <c r="A110" s="79"/>
+      <c r="B110" s="86" t="s">
+        <v>290</v>
+      </c>
+      <c r="C110" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="D110" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="E110" s="36"/>
+      <c r="F110" s="36" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="80"/>
-      <c r="B111" s="75" t="s">
-        <v>292</v>
-      </c>
-      <c r="C111" s="36" t="s">
+      <c r="A111" s="79"/>
+      <c r="B111" s="84"/>
+      <c r="C111" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D111" s="36" t="s">
+      <c r="D111" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36" t="s">
+      <c r="F111" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="80"/>
-      <c r="B112" s="76"/>
-      <c r="C112" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="F112" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="80"/>
+      <c r="A112" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B58:B67"/>
-    <mergeCell ref="B68:B77"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="B106:B110"/>
-    <mergeCell ref="A88:A113"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B105:B109"/>
+    <mergeCell ref="A87:A112"/>
     <mergeCell ref="A2:A32"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -4188,12 +4162,17 @@
     <mergeCell ref="A33:A54"/>
     <mergeCell ref="B33:B42"/>
     <mergeCell ref="B43:B54"/>
-    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="B84:B86"/>
     <mergeCell ref="B55:B57"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B97:B105"/>
-    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="B90:B95"/>
+    <mergeCell ref="B96:B104"/>
+    <mergeCell ref="B87:B89"/>
     <mergeCell ref="A55:A77"/>
+    <mergeCell ref="B58:B67"/>
+    <mergeCell ref="B68:B77"/>
+    <mergeCell ref="A78:A86"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B83"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
